--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484338_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484338_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.102</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8114</v>
+        <v>4.8425</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2906</v>
+        <v>3.3646</v>
       </c>
       <c r="G2" t="n">
         <v>2.5003</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>1.223</v>
+        <v>1.3281</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4566</v>
+        <v>0.5744</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6796</v>
+        <v>0.7536</v>
       </c>
       <c r="V2" t="n">
         <v>3.988</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7591</v>
+        <v>3.8093</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8844</v>
+        <v>3.6816</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1252</v>
+        <v>0.1278</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1867</v>
+        <v>2.5809</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9826</v>
+        <v>1.9333</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7959000000000001</v>
+        <v>0.6476</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0809</v>
+        <v>4.2991</v>
       </c>
       <c r="K3" t="n">
-        <v>2.067</v>
+        <v>2.4367</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0138</v>
+        <v>1.8624</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8941</v>
+        <v>-1.7182</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0844</v>
+        <v>-0.5034</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8097</v>
+        <v>-1.2148</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R3" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6543</v>
+        <v>0.8377</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8035</v>
+        <v>0.5545</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1492</v>
+        <v>0.2832</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4532</v>
+        <v>2.4563</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4888</v>
+        <v>2.4998</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0357</v>
+        <v>-0.0435</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5809</v>
+        <v>1.1867</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9333</v>
+        <v>1.9826</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6476</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2991</v>
+        <v>2.0809</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4367</v>
+        <v>2.067</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8624</v>
+        <v>0.0138</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7182</v>
+        <v>-0.8941</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5034</v>
+        <v>-0.0844</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2148</v>
+        <v>-0.8097</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5184</v>
+        <v>0.3514</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6382</v>
+        <v>0.419</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1198</v>
+        <v>-0.0675</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2375</v>
+        <v>0.1802</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1893</v>
+        <v>-0.0605</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9517</v>
+        <v>0.2407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1912</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1735</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0247</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.284</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3087</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8336</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6984</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1352</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5776</v>
+        <v>-0.0151</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0594</v>
+        <v>-0.0605</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5182</v>
+        <v>0.0454</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,37 +877,37 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.153</v>
+        <v>0.1019</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0605</v>
+        <v>0.0204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2135</v>
+        <v>0.0815</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.1237</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.2047</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.2047</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.2047</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0424</v>
+        <v>0.0303</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0519</v>
+        <v>0.0603</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7932</v>
+        <v>1.6109</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7412</v>
+        <v>-1.5506</v>
       </c>
       <c r="G7" t="n">
         <v>0.9421</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0269</v>
+        <v>-0.0186</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1899</v>
+        <v>0.0076</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2168</v>
+        <v>-0.0262</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2772</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0474</v>
+        <v>-0.3269</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0204</v>
+        <v>-0.1345</v>
       </c>
       <c r="F8" t="n">
-        <v>0.027</v>
+        <v>-0.1925</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1237</v>
+        <v>0.4849</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2047</v>
+        <v>0.4851</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0809</v>
+        <v>-0.0002</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0809</v>
+        <v>1.0438</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0438</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2047</v>
+        <v>-0.5589</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2047</v>
+        <v>-0.5587</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0242</v>
+        <v>-0.3625</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0605</v>
+        <v>-0.2015</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0363</v>
+        <v>-0.161</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6792</v>
+        <v>-0.6082</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2961</v>
+        <v>0.6431</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3831</v>
+        <v>-1.2513</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4849</v>
+        <v>0.1912</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4851</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0002</v>
+        <v>1.1735</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0438</v>
+        <v>1.0247</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0438</v>
+        <v>-0.284</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.3087</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5589</v>
+        <v>-0.8336</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5587</v>
+        <v>-0.6984</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0002</v>
+        <v>-0.1352</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
         <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7148</v>
+        <v>0.7318</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3631</v>
+        <v>0.5132</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3517</v>
+        <v>0.2186</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3321</v>
+        <v>-0.5545</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3321</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4557</v>
+        <v>-2.1229</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.032</v>
+        <v>-3.9715</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5763</v>
+        <v>1.8486</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7857</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0881</v>
+        <v>0.4209</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1432</v>
+        <v>0.2037</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0551</v>
+        <v>0.2173</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1933</v>
+        <v>-3.8877</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9291</v>
+        <v>-5.8685</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7358</v>
+        <v>1.9809</v>
       </c>
       <c r="G11" t="n">
         <v>1.6889</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3725</v>
+        <v>0.6782</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5201</v>
+        <v>0.5806</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1476</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.3869</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5527</v>
+        <v>-4.0073</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9806</v>
+        <v>-0.4351</v>
       </c>
       <c r="F12" t="n">
         <v>-3.5722</v>
@@ -1390,10 +1390,10 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2751</v>
+        <v>0.8205</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0989</v>
+        <v>0.4465</v>
       </c>
       <c r="U12" t="n">
         <v>0.374</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7343</v>
+        <v>-8.4627</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3751</v>
+        <v>-3.1035</v>
       </c>
       <c r="F13" t="n">
         <v>-5.3592</v>
@@ -1468,10 +1468,10 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4417</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3703</v>
+        <v>0.6419</v>
       </c>
       <c r="U13" t="n">
         <v>0.07140000000000001</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.8111</v>
+        <v>-4.600699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4859</v>
+        <v>-0.2752999999999979</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.325100000000001</v>
+        <v>-4.325200000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>6.439500000000001</v>
+        <v>6.439500000000002</v>
       </c>
       <c r="H14" t="n">
         <v>6.440299999999999</v>
@@ -1531,7 +1531,7 @@
         <v>-9.339</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.264</v>
+        <v>-3.263999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-6.074800000000001</v>
@@ -1546,13 +1546,13 @@
         <v>9.7669</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3056</v>
+        <v>5.515899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4086</v>
+        <v>3.6189</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8971</v>
+        <v>1.8972</v>
       </c>
       <c r="V14" t="n">
         <v>-2.882000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0481</v>
+        <v>4.4266</v>
       </c>
       <c r="E15" t="n">
         <v>4.5581</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.51</v>
+        <v>-0.1314</v>
       </c>
       <c r="G15" t="n">
         <v>0.3256</v>
@@ -1624,13 +1624,13 @@
         <v>2.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1324</v>
+        <v>-0.7538</v>
       </c>
       <c r="T15" t="n">
         <v>-0.341</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7914</v>
+        <v>-0.4128</v>
       </c>
       <c r="V15" t="n">
         <v>2.3154</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6916</v>
+        <v>2.6787</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5768</v>
+        <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1148</v>
+        <v>1.1187</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7665999999999999</v>
+        <v>1.0073</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8475</v>
+        <v>2.8279</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0809</v>
+        <v>-1.8206</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8063</v>
+        <v>3.2646</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1855</v>
+        <v>3.8706</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6208</v>
+        <v>-0.606</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5729</v>
+        <v>-2.2573</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.033</v>
+        <v>-1.0427</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5399</v>
+        <v>-1.2146</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9772999999999999</v>
+        <v>-0.7063</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7705</v>
+        <v>-0.6099</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2068</v>
+        <v>-0.0964</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>1.5964</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0541</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.5423</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6182</v>
+        <v>1.3247</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8521</v>
+        <v>-0.794</v>
       </c>
       <c r="F17" t="n">
-        <v>0.766</v>
+        <v>2.1186</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0073</v>
+        <v>-1.0057</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8279</v>
+        <v>-1.087</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8206</v>
+        <v>0.0813</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2646</v>
+        <v>-0.5816</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8706</v>
+        <v>-0.5283</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.606</v>
+        <v>-0.0533</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2573</v>
+        <v>-0.4241</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0427</v>
+        <v>-0.5587</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2146</v>
+        <v>0.1346</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9301</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7668</v>
+        <v>0.0262</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3177</v>
+        <v>-0.2943</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4491</v>
+        <v>0.3205</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5964</v>
+        <v>0.1554</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0541</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5423</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.784</v>
+        <v>1.1474</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1984</v>
+        <v>-0.9306</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9825</v>
+        <v>2.078</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0057</v>
+        <v>-1.7553</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.087</v>
+        <v>0.0241</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0813</v>
+        <v>-1.7793</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5816</v>
+        <v>-0.233</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5283</v>
+        <v>1.6807</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0533</v>
+        <v>-1.9137</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4241</v>
+        <v>-1.5223</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5587</v>
+        <v>-1.6567</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1346</v>
+        <v>0.1344</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-3.3208</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5144</v>
+        <v>-0.1588</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6987</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1843</v>
+        <v>-0.0675</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1554</v>
+        <v>3.2568</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>2.7145</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1219</v>
+        <v>0.5423</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7208</v>
+        <v>1.0609</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0318</v>
+        <v>2.247</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7525</v>
+        <v>-1.1861</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7553</v>
+        <v>-0.1506</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0241</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7793</v>
+        <v>0.4043</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.233</v>
+        <v>2.5809</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6807</v>
+        <v>0.5577</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9137</v>
+        <v>2.0233</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5223</v>
+        <v>-2.7316</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6567</v>
+        <v>-1.1125</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>-1.619</v>
       </c>
       <c r="P19" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.3208</v>
-      </c>
       <c r="R19" t="n">
-        <v>3.1255</v>
+        <v>2.7348</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5854</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1924</v>
+        <v>-0.3609</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.393</v>
+        <v>-0.4582</v>
       </c>
       <c r="V19" t="n">
-        <v>3.2568</v>
+        <v>-0.5088</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7145</v>
+        <v>0.2224</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5423</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6084000000000001</v>
+        <v>1.0032</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1459</v>
+        <v>0.9701</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5375</v>
+        <v>0.0331</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1506</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.8475</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4043</v>
+        <v>0.0809</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5809</v>
+        <v>0.8063</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5577</v>
+        <v>0.1855</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0233</v>
+        <v>0.6208</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7316</v>
+        <v>-1.5729</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1125</v>
+        <v>-1.033</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.619</v>
+        <v>-0.5399</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2716</v>
+        <v>0.2889</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4621</v>
+        <v>0.1638</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8095</v>
+        <v>0.1251</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5088</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7312</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1541</v>
+        <v>0.1828</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1203</v>
+        <v>0.3793</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2744</v>
+        <v>-0.1965</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.027</v>
+        <v>-0.598</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6877</v>
+        <v>-0.0987</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6607</v>
+        <v>-0.4992</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1424</v>
+        <v>0.0814</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2638</v>
+        <v>0.0409</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1214</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1154</v>
+        <v>-0.6793</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4239</v>
+        <v>-0.1397</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5393</v>
+        <v>-0.5397</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1142</v>
+        <v>-0.0825</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2175</v>
+        <v>0.0207</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8968</v>
+        <v>-0.1032</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0467</v>
+        <v>-0.4566</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1771</v>
+        <v>-1.3225</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2238</v>
+        <v>0.8659</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.598</v>
+        <v>-1.027</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0987</v>
+        <v>-1.6877</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4992</v>
+        <v>0.6607</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0814</v>
+        <v>-1.1424</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0409</v>
+        <v>-1.2638</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.1214</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6793</v>
+        <v>0.1154</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1397</v>
+        <v>-0.4239</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5397</v>
+        <v>0.5393</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.312</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1816</v>
+        <v>0.0152</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1304</v>
+        <v>0.4883</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9475</v>
+        <v>-2.029</v>
       </c>
       <c r="E23" t="n">
-        <v>1.465</v>
+        <v>-2.7959</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4125</v>
+        <v>0.767</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1855</v>
+        <v>-2.2836</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7657</v>
+        <v>-2.0404</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5800999999999999</v>
+        <v>-0.2432</v>
       </c>
       <c r="J23" t="n">
-        <v>2.546</v>
+        <v>-0.8359</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6165</v>
+        <v>-0.9977</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9295</v>
+        <v>0.1619</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7316</v>
+        <v>-1.4478</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3822</v>
+        <v>-1.0427</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3494</v>
+        <v>-0.4051</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5395</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9525</v>
+        <v>-0.976</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0677</v>
+        <v>-0.4559</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1152</v>
+        <v>-0.5201</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1052</v>
+        <v>-0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8198</v>
+        <v>-2.1793</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0993</v>
+        <v>0.4538</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2794</v>
+        <v>-2.6331</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2836</v>
+        <v>-0.1855</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0404</v>
+        <v>-0.7657</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2432</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8359</v>
+        <v>2.546</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9977</v>
+        <v>0.6165</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1619</v>
+        <v>1.9295</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4478</v>
+        <v>-2.7316</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0427</v>
+        <v>-1.3822</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4051</v>
+        <v>-1.3494</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7668</v>
+        <v>-0.2792</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7592</v>
+        <v>0.0566</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0076</v>
+        <v>-0.3358</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3321</v>
+        <v>-2.1052</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.8112</v>
+        <v>7.159400000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>4.325200000000001</v>
+        <v>4.325299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4858</v>
+        <v>2.8342</v>
       </c>
       <c r="G25" t="n">
         <v>-6.4394</v>
@@ -2374,7 +2374,7 @@
         <v>-6.4402</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0008999999999998731</v>
+        <v>0.0008999999999995678</v>
       </c>
       <c r="J25" t="n">
         <v>9.338800000000001</v>
@@ -2398,22 +2398,22 @@
         <v>13.6741</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.767100000000001</v>
+        <v>-9.767099999999999</v>
       </c>
       <c r="R25" t="n">
         <v>23.4411</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.305400000000001</v>
+        <v>-2.9571</v>
       </c>
       <c r="T25" t="n">
         <v>-1.897</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.4083</v>
+        <v>-1.0601</v>
       </c>
       <c r="V25" t="n">
-        <v>2.882</v>
+        <v>2.882000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>6.650600000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484338_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484338_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +819,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1802</v>
+        <v>1.8349</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0605</v>
+        <v>1.8349</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2407</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.8349</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.2279</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.8349</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.2279</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -835,22 +855,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0151</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0454</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,12 +880,17 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,37 +902,37 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1019</v>
+        <v>0.1802</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0204</v>
+        <v>-0.0605</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0815</v>
+        <v>0.2407</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1237</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -922,13 +947,13 @@
         <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0303</v>
+        <v>-0.0151</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0603</v>
+        <v>0.1019</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6109</v>
+        <v>0.0204</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5506</v>
+        <v>0.0815</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9421</v>
+        <v>-0.1237</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7516</v>
+        <v>-0.2047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8095</v>
+        <v>0.0809</v>
       </c>
       <c r="J7" t="n">
-        <v>2.58</v>
+        <v>0.0809</v>
       </c>
       <c r="K7" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6379</v>
+        <v>-0.2047</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8283</v>
+        <v>-0.2047</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8095</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0186</v>
+        <v>0.0303</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0076</v>
+        <v>-0.0605</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0262</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3269</v>
+        <v>0.0603</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1345</v>
+        <v>1.6109</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1925</v>
+        <v>-1.5506</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4849</v>
+        <v>0.9421</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4851</v>
+        <v>1.7516</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0002</v>
+        <v>-0.8095</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0438</v>
+        <v>2.58</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0438</v>
+        <v>2.58</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5589</v>
+        <v>-1.6379</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5587</v>
+        <v>-0.8283</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>-0.8095</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3625</v>
+        <v>-0.0186</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2015</v>
+        <v>0.0076</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.161</v>
+        <v>-0.0262</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6082</v>
+        <v>-0.3269</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6431</v>
+        <v>-0.1345</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2513</v>
+        <v>-0.1925</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1912</v>
+        <v>0.4849</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0.4851</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1735</v>
+        <v>-0.0002</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0247</v>
+        <v>1.0438</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.284</v>
+        <v>1.0438</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3087</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8336</v>
+        <v>-0.5589</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6984</v>
+        <v>-0.5587</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1352</v>
+        <v>-0.0002</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.9767</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
         <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7318</v>
+        <v>-0.3625</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5132</v>
+        <v>-0.2015</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2186</v>
+        <v>-0.161</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5545</v>
+        <v>0.3321</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8317</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1229</v>
+        <v>-0.6082</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9715</v>
+        <v>0.6431</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8486</v>
+        <v>-1.2513</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7857</v>
+        <v>0.1912</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1179</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9036999999999999</v>
+        <v>1.1735</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2451</v>
+        <v>1.0247</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.284</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.3087</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4593</v>
+        <v>-0.8336</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7294</v>
+        <v>-0.6984</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.27</v>
+        <v>-0.1352</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4209</v>
+        <v>0.7318</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2037</v>
+        <v>0.5132</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2173</v>
+        <v>0.2186</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1317,72 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8877</v>
+        <v>-2.1229</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8685</v>
+        <v>-3.9715</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9809</v>
+        <v>1.8486</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6889</v>
+        <v>-0.7857</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0801</v>
+        <v>0.1179</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3912</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3646</v>
+        <v>-1.2451</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3507</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0138</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3243</v>
+        <v>0.4593</v>
       </c>
       <c r="N11" t="n">
         <v>0.7294</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4051</v>
+        <v>-0.27</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.6417</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.8137</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6782</v>
+        <v>0.4209</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5806</v>
+        <v>0.2037</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.2173</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1407,11 +1462,16 @@
       <c r="X12" t="n">
         <v>-3.6559</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4627</v>
+        <v>-5.7226</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1035</v>
+        <v>-7.7035</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.3592</v>
+        <v>1.9809</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.9453</v>
+        <v>-0.1461</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9489</v>
+        <v>0.8522</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9964</v>
+        <v>-0.9982</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1391</v>
+        <v>-0.4704</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0473</v>
+        <v>0.1228</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1863</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.8063</v>
+        <v>0.3243</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9962</v>
+        <v>0.7294</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8101</v>
+        <v>-0.4051</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1255</v>
+        <v>-6.6417</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.1022</v>
+        <v>-7.8137</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.6782</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6419</v>
+        <v>0.5806</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1052</v>
+        <v>0.3869</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.601</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.600699999999999</v>
+        <v>-8.4627</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2752999999999979</v>
+        <v>-3.1035</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.325200000000001</v>
+        <v>-5.3592</v>
       </c>
       <c r="G14" t="n">
-        <v>6.439500000000002</v>
+        <v>-3.9453</v>
       </c>
       <c r="H14" t="n">
-        <v>6.440299999999999</v>
+        <v>-1.9489</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0009999999999998899</v>
+        <v>-1.9964</v>
       </c>
       <c r="J14" t="n">
-        <v>15.7783</v>
+        <v>-1.1391</v>
       </c>
       <c r="K14" t="n">
-        <v>9.704400000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="L14" t="n">
-        <v>6.0737</v>
+        <v>-1.1863</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.339</v>
+        <v>-2.8063</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.263999999999999</v>
+        <v>-1.9962</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.074800000000001</v>
+        <v>-0.8101</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.6741</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q14" t="n">
-        <v>-23.4412</v>
+        <v>-4.1022</v>
       </c>
       <c r="R14" t="n">
-        <v>9.7669</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>5.515899999999999</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6189</v>
+        <v>0.6419</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8972</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.882000000000001</v>
+        <v>-2.1052</v>
       </c>
       <c r="W14" t="n">
-        <v>3.7686</v>
+        <v>1.4959</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.6505</v>
+        <v>-3.601</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4266</v>
+        <v>-4.600699999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5581</v>
+        <v>-0.2754000000000008</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1314</v>
+        <v>-4.325200000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3256</v>
+        <v>6.439400000000003</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2103</v>
+        <v>6.440300000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5359</v>
+        <v>-0.001000000000000112</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8525</v>
+        <v>15.7782</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.898</v>
+        <v>9.7044</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7505</v>
+        <v>6.0737</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5269</v>
+        <v>-9.338999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3123</v>
+        <v>-3.264</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2146</v>
+        <v>-6.0748</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5395</v>
+        <v>-13.6741</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3907</v>
+        <v>-23.4412</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9301</v>
+        <v>9.766899999999998</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7538</v>
+        <v>5.515899999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.341</v>
+        <v>3.6189</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4128</v>
+        <v>1.8972</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3154</v>
+        <v>-2.882000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>3.7686</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1219</v>
-      </c>
+        <v>-6.6505</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6787</v>
+        <v>4.4266</v>
       </c>
       <c r="E16" t="n">
-        <v>1.56</v>
+        <v>4.5581</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1187</v>
+        <v>-0.1314</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0073</v>
+        <v>0.3256</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8279</v>
+        <v>-2.2103</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8206</v>
+        <v>2.5359</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2646</v>
+        <v>2.8525</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8706</v>
+        <v>-0.898</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.606</v>
+        <v>3.7505</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2573</v>
+        <v>-2.5269</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0427</v>
+        <v>-1.3123</v>
       </c>
       <c r="O16" t="n">
         <v>-1.2146</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="R16" t="n">
         <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7063</v>
+        <v>-0.7538</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6099</v>
+        <v>-0.341</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0964</v>
+        <v>-0.4128</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5964</v>
+        <v>2.3154</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0541</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5423</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3247</v>
+        <v>2.6787</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.794</v>
+        <v>1.56</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1186</v>
+        <v>1.1187</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0057</v>
+        <v>1.0073</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.087</v>
+        <v>2.8279</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0813</v>
+        <v>-1.8206</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5816</v>
+        <v>3.2646</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5283</v>
+        <v>3.8706</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0533</v>
+        <v>-0.606</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4241</v>
+        <v>-2.2573</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5587</v>
+        <v>-1.0427</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>-1.2146</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0262</v>
+        <v>-0.7063</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2943</v>
+        <v>-0.6099</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3205</v>
+        <v>-0.0964</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1554</v>
+        <v>1.5964</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>1.0541</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1219</v>
+        <v>0.5423</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1474</v>
+        <v>1.521</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9306</v>
+        <v>1.521</v>
       </c>
       <c r="F18" t="n">
-        <v>2.078</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7553</v>
+        <v>1.521</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0241</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7793</v>
+        <v>1.214</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.233</v>
+        <v>1.521</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6807</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9137</v>
+        <v>1.214</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5223</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6567</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1588</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0675</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.2568</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5423</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0609</v>
+        <v>1.3247</v>
       </c>
       <c r="E19" t="n">
-        <v>2.247</v>
+        <v>-0.794</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1861</v>
+        <v>2.1186</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1506</v>
+        <v>-1.0057</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-1.087</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4043</v>
+        <v>0.0813</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5809</v>
+        <v>-0.5816</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5577</v>
+        <v>-0.5283</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0233</v>
+        <v>-0.0533</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7316</v>
+        <v>-0.4241</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1125</v>
+        <v>-0.5587</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.619</v>
+        <v>0.1346</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8191000000000001</v>
+        <v>0.0262</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3609</v>
+        <v>-0.2943</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4582</v>
+        <v>0.3205</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5088</v>
+        <v>0.1554</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2224</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7312</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0032</v>
+        <v>1.1474</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9701</v>
+        <v>-0.9306</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0331</v>
+        <v>2.078</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-1.7553</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8475</v>
+        <v>0.0241</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0809</v>
+        <v>-1.7793</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8063</v>
+        <v>-0.233</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1855</v>
+        <v>1.6807</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6208</v>
+        <v>-1.9137</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5729</v>
+        <v>-1.5223</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.033</v>
+        <v>-1.6567</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5399</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.3208</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>3.1255</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2889</v>
+        <v>-0.1588</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1638</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1251</v>
+        <v>-0.0675</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>3.2568</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0.5423</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1828</v>
+        <v>1.0609</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3793</v>
+        <v>2.247</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1965</v>
+        <v>-1.1861</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.598</v>
+        <v>-0.1506</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0987</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4992</v>
+        <v>0.4043</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0814</v>
+        <v>2.5809</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>0.5577</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>2.0233</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6793</v>
+        <v>-2.7316</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1397</v>
+        <v>-1.1125</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5397</v>
+        <v>-1.619</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0825</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0207</v>
+        <v>-0.3609</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1032</v>
+        <v>-0.4582</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>-0.5088</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0.2224</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4566</v>
+        <v>1.0032</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3225</v>
+        <v>0.9701</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8659</v>
+        <v>0.0331</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.027</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6877</v>
+        <v>-0.8475</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6607</v>
+        <v>0.0809</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1424</v>
+        <v>0.8063</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2638</v>
+        <v>0.1855</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>0.6208</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1154</v>
+        <v>-1.5729</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4239</v>
+        <v>-1.033</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5393</v>
+        <v>-0.5399</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.2889</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0152</v>
+        <v>0.1638</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4883</v>
+        <v>0.1251</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.029</v>
+        <v>0.1828</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7959</v>
+        <v>0.3793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.767</v>
+        <v>-0.1965</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2836</v>
+        <v>-0.598</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0404</v>
+        <v>-0.0987</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2432</v>
+        <v>-0.4992</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8359</v>
+        <v>0.0814</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9977</v>
+        <v>0.0409</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4478</v>
+        <v>-0.6793</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0427</v>
+        <v>-0.1397</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4051</v>
+        <v>-0.5397</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7348</v>
+        <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.976</v>
+        <v>-0.0825</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4559</v>
+        <v>0.0207</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5201</v>
+        <v>-0.1032</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1793</v>
+        <v>-0.4566</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4538</v>
+        <v>-1.3225</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6331</v>
+        <v>0.8659</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1855</v>
+        <v>-1.027</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7657</v>
+        <v>-1.6877</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6607</v>
       </c>
       <c r="J24" t="n">
-        <v>2.546</v>
+        <v>-1.1424</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6165</v>
+        <v>-1.2638</v>
       </c>
       <c r="L24" t="n">
-        <v>1.9295</v>
+        <v>0.1214</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7316</v>
+        <v>0.1154</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3822</v>
+        <v>-0.4239</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3494</v>
+        <v>0.5393</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2792</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0566</v>
+        <v>0.0152</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3358</v>
+        <v>0.4883</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1052</v>
+        <v>-1.4959</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1052</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.159400000000002</v>
+        <v>-2.029</v>
       </c>
       <c r="E25" t="n">
-        <v>4.325299999999999</v>
+        <v>-2.7959</v>
       </c>
       <c r="F25" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.2836</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.0404</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.2432</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.8359</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.9977</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.4478</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.0427</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.976</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4559</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.5201</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P. CAMPANA SOLER</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.7002</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.0671</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.6331</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.7065</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.0727</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.6338</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.0251</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.7156</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.7316</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.3822</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2792</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.3358</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484338_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7.159500000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.3254</v>
+      </c>
+      <c r="F27" t="n">
         <v>2.8342</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>-6.4394</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>-6.4402</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.0008999999999995678</v>
-      </c>
-      <c r="J25" t="n">
-        <v>9.338800000000001</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="I27" t="n">
+        <v>0.0009999999999997788</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.338900000000001</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.2641</v>
       </c>
-      <c r="L25" t="n">
-        <v>6.0749</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="L27" t="n">
+        <v>6.075000000000001</v>
+      </c>
+      <c r="M27" t="n">
         <v>-15.7784</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-9.7044</v>
       </c>
-      <c r="O25" t="n">
-        <v>-6.074</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="O27" t="n">
+        <v>-6.074000000000001</v>
+      </c>
+      <c r="P27" t="n">
         <v>13.6741</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-9.767099999999999</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>23.4411</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>-2.9571</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>-1.897</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>-1.0601</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>2.882000000000001</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>6.650600000000001</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-3.7687</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
